--- a/data/trans_orig/IP16A11_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP16A11_2023-Habitat-trans_orig.xlsx
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5391</t>
+          <t>5207</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13023</t>
+          <t>13435</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>48,34%</t>
+          <t>49,87%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1002</t>
+          <t>1017</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6809</t>
+          <t>6188</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7103</t>
+          <t>7405</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16501</t>
+          <t>17536</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>31,82%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13915</t>
+          <t>13503</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21547</t>
+          <t>21731</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>51,66%</t>
+          <t>50,13%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>79,99%</t>
+          <t>80,67%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>21358</t>
+          <t>21979</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>27165</t>
+          <t>27150</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>75,82%</t>
+          <t>78,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>38604</t>
+          <t>37569</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>48002</t>
+          <t>47700</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>70,06%</t>
+          <t>68,18%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>87,11%</t>
+          <t>86,56%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8533</t>
+          <t>9045</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20920</t>
+          <t>21320</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>46,72%</t>
+          <t>47,61%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14096</t>
+          <t>14229</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>27781</t>
+          <t>27250</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>22,3%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>43,54%</t>
+          <t>42,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>27156</t>
+          <t>26453</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>44448</t>
+          <t>44597</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>40,93%</t>
+          <t>41,07%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>23862</t>
+          <t>23462</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>36249</t>
+          <t>35737</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>53,28%</t>
+          <t>52,39%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>80,94%</t>
+          <t>79,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>36028</t>
+          <t>36559</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>49713</t>
+          <t>49580</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>56,46%</t>
+          <t>57,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>77,91%</t>
+          <t>77,7%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>64143</t>
+          <t>63994</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>81435</t>
+          <t>82138</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>59,07%</t>
+          <t>58,93%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>74,99%</t>
+          <t>75,64%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7871</t>
+          <t>8577</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>40748</t>
+          <t>41233</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>52,87%</t>
+          <t>53,5%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17320</t>
+          <t>17812</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>32580</t>
+          <t>32362</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,43%</t>
+          <t>31,29%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>57,23%</t>
+          <t>56,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>27189</t>
+          <t>24709</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>67134</t>
+          <t>66633</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>50,1%</t>
+          <t>49,73%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>36323</t>
+          <t>35838</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>69200</t>
+          <t>68494</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>47,13%</t>
+          <t>46,5%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>89,79%</t>
+          <t>88,87%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>24343</t>
+          <t>24561</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>39603</t>
+          <t>39111</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>42,77%</t>
+          <t>43,15%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>69,57%</t>
+          <t>68,71%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>66860</t>
+          <t>67361</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>106805</t>
+          <t>109285</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>49,9%</t>
+          <t>50,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>79,71%</t>
+          <t>81,56%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5446</t>
+          <t>5176</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13254</t>
+          <t>13205</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>43,37%</t>
+          <t>43,21%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6282</t>
+          <t>5498</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15558</t>
+          <t>14898</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>46,02%</t>
+          <t>44,07%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>13544</t>
+          <t>13349</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>26038</t>
+          <t>25889</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>40,45%</t>
+          <t>40,22%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>17307</t>
+          <t>17356</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>25115</t>
+          <t>25385</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>56,63%</t>
+          <t>56,79%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,18%</t>
+          <t>83,06%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>18251</t>
+          <t>18911</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>27527</t>
+          <t>28311</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>53,98%</t>
+          <t>55,93%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>81,42%</t>
+          <t>83,74%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>38332</t>
+          <t>38481</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>50826</t>
+          <t>51021</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>59,55%</t>
+          <t>59,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,96%</t>
+          <t>79,26%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>33793</t>
+          <t>35717</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>72844</t>
+          <t>73114</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>40,62%</t>
+          <t>40,77%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>48224</t>
+          <t>47794</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>71335</t>
+          <t>69961</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>26,16%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>39,04%</t>
+          <t>38,29%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>86219</t>
+          <t>90094</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>133730</t>
+          <t>134078</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>37,03%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>106508</t>
+          <t>106238</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>145559</t>
+          <t>143635</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>59,38%</t>
+          <t>59,23%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>81,16%</t>
+          <t>80,09%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>111374</t>
+          <t>112748</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>134485</t>
+          <t>134915</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>60,96%</t>
+          <t>61,71%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>73,61%</t>
+          <t>73,84%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>228331</t>
+          <t>227983</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>275842</t>
+          <t>271967</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>63,06%</t>
+          <t>62,97%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>76,19%</t>
+          <t>75,12%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP16A11_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP16A11_2023-Habitat-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2767</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>6518</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>11,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>3,75%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>25,92%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>8775</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>5207</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>13435</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>32,57%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>19,33%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>49,87%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2911</t>
+          <t>9465</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1017</t>
+          <t>5724</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6188</t>
+          <t>13684</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>34,57%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>49,98%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>11686</t>
+          <t>12232</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7405</t>
+          <t>7982</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17536</t>
+          <t>17793</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>31,82%</t>
+          <t>33,87%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>22381</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>18630</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>24204</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>89,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>74,08%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>96,25%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>18163</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>13503</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>21731</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>67,43%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>50,13%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>80,67%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>25256</t>
+          <t>17917</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>21979</t>
+          <t>13698</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>27150</t>
+          <t>21658</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>89,66%</t>
+          <t>65,43%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>78,03%</t>
+          <t>50,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>79,1%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>43419</t>
+          <t>40298</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>37569</t>
+          <t>34737</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>47700</t>
+          <t>44548</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>78,79%</t>
+          <t>76,71%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>68,18%</t>
+          <t>66,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,56%</t>
+          <t>84,8%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>25148</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>25148</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>25148</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>26938</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>26938</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>26938</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>28167</t>
+          <t>27382</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>28167</t>
+          <t>27382</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>28167</t>
+          <t>27382</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>55105</t>
+          <t>52530</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>55105</t>
+          <t>52530</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>55105</t>
+          <t>52530</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>17868</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>12140</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>24179</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>31,65%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>21,5%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>42,83%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>14967</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>9045</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>21320</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>33,42%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>20,2%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>47,61%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>20301</t>
+          <t>13401</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14229</t>
+          <t>8617</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>27250</t>
+          <t>18276</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>36,5%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>42,71%</t>
+          <t>49,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>35268</t>
+          <t>31269</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>26453</t>
+          <t>23607</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>44597</t>
+          <t>39296</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>33,56%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>41,07%</t>
+          <t>42,18%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>38590</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>32279</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>44318</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>68,35%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>57,17%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>78,5%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>29815</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>23462</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>35737</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>66,58%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>52,39%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>79,8%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>43508</t>
+          <t>23309</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>36559</t>
+          <t>18434</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>49580</t>
+          <t>28093</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>68,19%</t>
+          <t>63,5%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>57,29%</t>
+          <t>50,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>77,7%</t>
+          <t>76,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>73323</t>
+          <t>61899</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>63994</t>
+          <t>53872</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>82138</t>
+          <t>69561</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>67,52%</t>
+          <t>66,44%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>58,93%</t>
+          <t>57,82%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>75,64%</t>
+          <t>74,66%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>56458</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>56458</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>56458</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>44782</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>44782</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>44782</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>63809</t>
+          <t>36710</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>63809</t>
+          <t>36710</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>63809</t>
+          <t>36710</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>108591</t>
+          <t>93168</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>108591</t>
+          <t>93168</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>108591</t>
+          <t>93168</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>21912</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>14453</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>28527</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>41,85%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>27,61%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>54,49%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>24489</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>8577</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>41233</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>31,77%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>11,13%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>53,5%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>25188</t>
+          <t>24522</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17812</t>
+          <t>18371</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>32362</t>
+          <t>31023</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>44,25%</t>
+          <t>48,25%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>31,29%</t>
+          <t>36,14%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>56,85%</t>
+          <t>61,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>49676</t>
+          <t>46434</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>24709</t>
+          <t>36857</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>66633</t>
+          <t>57406</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>37,07%</t>
+          <t>45,0%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>35,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>49,73%</t>
+          <t>55,64%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>30443</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>23828</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>37902</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>58,15%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>45,51%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>72,39%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>52582</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>35838</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>68494</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>68,23%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>46,5%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>88,87%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>31735</t>
+          <t>26304</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>24561</t>
+          <t>19803</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>39111</t>
+          <t>32455</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>55,75%</t>
+          <t>51,75%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>43,15%</t>
+          <t>38,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>68,71%</t>
+          <t>63,86%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>84318</t>
+          <t>56747</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>67361</t>
+          <t>45775</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>109285</t>
+          <t>66324</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>62,93%</t>
+          <t>55,0%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>50,27%</t>
+          <t>44,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>81,56%</t>
+          <t>64,28%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>52355</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>52355</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>52355</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>73</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>77071</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>77071</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>77071</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>56923</t>
+          <t>50826</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>56923</t>
+          <t>50826</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>56923</t>
+          <t>50826</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>133994</t>
+          <t>103181</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>133994</t>
+          <t>103181</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>133994</t>
+          <t>103181</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>10305</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>5789</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>15065</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>32,7%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>18,37%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>47,8%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>8774</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>5176</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>13205</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>28,71%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>16,94%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>43,21%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>10169</t>
+          <t>8816</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5498</t>
+          <t>4920</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14898</t>
+          <t>12733</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>29,66%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>44,07%</t>
+          <t>42,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>18943</t>
+          <t>19121</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>13349</t>
+          <t>13260</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>25889</t>
+          <t>25074</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>31,22%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>40,22%</t>
+          <t>40,94%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>21212</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>16452</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>25728</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>67,3%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>52,2%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>81,63%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>21787</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>17356</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>25385</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>71,29%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>56,79%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>83,06%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>23640</t>
+          <t>20907</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>18911</t>
+          <t>16990</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>28311</t>
+          <t>24803</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>69,92%</t>
+          <t>70,34%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>55,93%</t>
+          <t>57,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,74%</t>
+          <t>83,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>45427</t>
+          <t>42119</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>38481</t>
+          <t>36166</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>51021</t>
+          <t>47980</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>70,57%</t>
+          <t>68,78%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>59,78%</t>
+          <t>59,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>79,26%</t>
+          <t>78,35%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>31517</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>31517</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>31517</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>30561</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>30561</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>30561</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>33809</t>
+          <t>29723</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>33809</t>
+          <t>29723</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>33809</t>
+          <t>29723</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>64370</t>
+          <t>61240</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>64370</t>
+          <t>61240</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>64370</t>
+          <t>61240</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>52852</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>42683</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>63754</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>31,94%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>25,79%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>38,53%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>57005</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>35717</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>73114</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>31,78%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>19,91%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>40,77%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>58569</t>
+          <t>56204</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>47794</t>
+          <t>47419</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>69961</t>
+          <t>66158</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>38,86%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>32,78%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>38,29%</t>
+          <t>45,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>115574</t>
+          <t>109056</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>90094</t>
+          <t>93456</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>134078</t>
+          <t>121778</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>35,17%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>30,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>37,03%</t>
+          <t>39,27%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>112627</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>101725</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>122796</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>68,06%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>61,47%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>74,21%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>140</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>122347</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>106238</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>143635</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>68,22%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>59,23%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>80,09%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>171</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>124140</t>
+          <t>88437</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>112748</t>
+          <t>78483</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>134915</t>
+          <t>97222</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>67,94%</t>
+          <t>61,14%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>61,71%</t>
+          <t>54,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>73,84%</t>
+          <t>67,22%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>246487</t>
+          <t>201064</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>227983</t>
+          <t>188342</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>271967</t>
+          <t>216664</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>68,08%</t>
+          <t>64,83%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>62,97%</t>
+          <t>60,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>75,12%</t>
+          <t>69,86%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>165479</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>165479</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>165479</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>229</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>179352</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>179352</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>179352</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>251</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>182709</t>
+          <t>144641</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>182709</t>
+          <t>144641</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>182709</t>
+          <t>144641</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>362061</t>
+          <t>310120</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>362061</t>
+          <t>310120</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>362061</t>
+          <t>310120</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
